--- a/excel/existenciasOptex.xlsx
+++ b/excel/existenciasOptex.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,16 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Linea</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Existencias</t>
         </is>
       </c>
@@ -448,65 +458,125 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>NF-TB01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>NF-DB01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>C2RP-350N</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>CDD-11N-IR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>Z2D-80CN4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -515,22 +585,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50212</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>BGS-Y8CP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Z2R-400CP4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -539,310 +629,570 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>BGS-Z30CP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>ZR-L1000CP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>C2DM-11N</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>ZR-QX200CP4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Z2D-80P</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>BGS-ZL30CP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Z2D-80N</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>BGS-2V100CP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Z2R-400P</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Z3R-400N</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>50212</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>V-61</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>BEF-W100-B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>YD-15N</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>EL-08PL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>56516</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>NF-DT01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>C2DP-80N</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>NF-DM01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>BGS-Z30CN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>C2RM-F400CP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>V2T-7000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>ZR-QX200N</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>ET-S500NL3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>V2R-1200CDP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>53138</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>NF-TR14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>V2R-1200</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
+        <is>
+          <t>BGS-Y8CN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -851,48 +1201,88 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>C2RP-F400CP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>BGF-TN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>YD-15N-M12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>C2RM-SF400CP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -904,6 +1294,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>NF-TR03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
@@ -911,10 +1311,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>EL-30PD</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -923,58 +1333,108 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>NF-DR01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>C2RP-F400N</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>ZR-M550P-M12</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>VD-250CP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
+        <is>
+          <t>NF-DT02</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -983,10 +1443,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>S2R-350CP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -995,10 +1465,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17093</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
+        <is>
+          <t>BGS-Z10CN</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1007,36 +1487,66 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Z2T-2000CP4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>VR-1000T</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>C2DP-80CP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1048,6 +1558,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>NF-TS08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
@@ -1055,10 +1575,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
+        <is>
+          <t>ZD-M80N</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1067,10 +1597,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
+        <is>
+          <t>D2RF-TP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1079,10 +1619,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
+        <is>
+          <t>NF-DK04Z</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1091,10 +1641,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
+        <is>
+          <t>C2RP-350CP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1103,36 +1663,66 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Z2R-400N</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>KR-250CP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>BGS-Z30P</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1144,6 +1734,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>JT-H1000CPR</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
@@ -1151,10 +1751,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
+        <is>
+          <t>DR-Q400TCP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1163,46 +1773,86 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>CRD-400P-R</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>C2DP-40N</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Z3R-Q200CP4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
+        <is>
+          <t>NF25-T</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1216,6 +1866,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>NF-DV02</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
@@ -1223,10 +1883,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
+        <is>
+          <t>CDD-100N-IR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1235,10 +1905,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
+        <is>
+          <t>Z3D-L09N</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1247,10 +1927,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
+        <is>
+          <t>V4R-1200</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1259,10 +1949,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
+        <is>
+          <t>BGS-S08CP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1276,6 +1976,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>BRF-CN</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
@@ -1283,10 +1993,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
+        <is>
+          <t>BGS-Y8P-M12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1295,10 +2015,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
+        <is>
+          <t>C2DP-80P</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1307,10 +2037,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
+        <is>
+          <t>C2DP-40CP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1319,10 +2059,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
+        <is>
+          <t>CRD-400N-R</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1331,46 +2081,86 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>C2DM-11P</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>54209</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>BGS-2V100CN</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>NF-TR02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
+        <is>
+          <t>YT-1180CP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1384,6 +2174,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>D3RF-TDP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
@@ -1391,10 +2191,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
+        <is>
+          <t>V2R-1200DP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1403,10 +2213,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
+        <is>
+          <t>D1RF-T</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1415,10 +2235,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
+        <is>
+          <t>BGS-ZL30CN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1427,10 +2257,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
+        <is>
+          <t>DSL-DH06-G1M8</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1439,10 +2279,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
+        <is>
+          <t>YT-1180N</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1451,10 +2301,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
+        <is>
+          <t>JR-H300N</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1463,10 +2323,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>54209</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
+        <is>
+          <t>PT-2LD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1475,10 +2345,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
+        <is>
+          <t>C2DP-11P</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1487,46 +2367,86 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>C2RP-F400CN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>V-42</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>C2DP-40P</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
+        <is>
+          <t>VD-300T</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1535,10 +2455,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
+        <is>
+          <t>ZR-L1000N</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1547,10 +2477,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
+        <is>
+          <t>CDD-11P-R</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1559,10 +2499,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>19566</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
+        <is>
+          <t>BGF-TP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1571,10 +2521,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
+        <is>
+          <t>CDD-100P-IR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1583,10 +2543,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
+        <is>
+          <t>DM-18TN</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1595,10 +2565,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
+        <is>
+          <t>BGS-ZL10CP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1607,10 +2587,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
+        <is>
+          <t>NF-DS06</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1619,10 +2609,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
+        <is>
+          <t>BEF-W100-A</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1631,10 +2631,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
+        <is>
+          <t>DOL-1205-G02M 6008899</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1643,10 +2653,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
+        <is>
+          <t>CD33-250PA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1655,10 +2675,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
+        <is>
+          <t>ED-S30PL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1667,10 +2697,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
+        <is>
+          <t>V2R-1200CDN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1679,10 +2719,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
+        <is>
+          <t>ZR-350CN</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1691,10 +2741,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
+        <is>
+          <t>C2RP-S350CP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1703,10 +2763,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
+        <is>
+          <t>NF-TA01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1715,10 +2785,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
+        <is>
+          <t>BGS-2S30CN</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1727,10 +2807,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
+        <is>
+          <t>ZR-M550P</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1739,10 +2829,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
+        <is>
+          <t>ET-S500PL</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1751,10 +2851,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
+        <is>
+          <t>ST-400P</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1763,130 +2873,240 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>BGS-30N</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ZD-L40CP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C2TM-2000CP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>51652</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>EL-08PD</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C2DM-80CP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>C2DM-40CN</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Z2T-2000P</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>VR-1000</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ET-500NL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Z2D-80CP4</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
+        <is>
+          <t>BRF-CP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1895,10 +3115,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
+        <is>
+          <t>C2RP-S350P</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1907,10 +3137,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
+        <is>
+          <t>MVS-C5S</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1919,10 +3159,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
+        <is>
+          <t>BGS-S08N</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1931,10 +3181,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
+        <is>
+          <t>BGS-S08P</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1943,10 +3203,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
+        <is>
+          <t>BGS-DL30N</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1955,10 +3225,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
+        <is>
+          <t>BGS-ZL10P</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1967,10 +3247,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
+        <is>
+          <t>CDD-100N-R</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1979,10 +3269,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
+        <is>
+          <t>DR-Q150TCP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1991,10 +3291,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
+        <is>
+          <t>BGS-ZL30P</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2003,10 +3313,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
+        <is>
+          <t>Z3R-400CP4</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2015,10 +3335,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
+        <is>
+          <t>PL10F</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2027,10 +3357,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
+        <is>
+          <t>CVS2-P20-RA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2039,10 +3379,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
+        <is>
+          <t>DM-18TCP</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2051,10 +3401,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
+        <is>
+          <t>BGS-Z10P</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2063,10 +3423,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
+        <is>
+          <t>JD-HW08P</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2075,10 +3445,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
+        <is>
+          <t>SR-Q50PW</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2087,178 +3467,328 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NF-TJ01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>SA-80T-2A</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>51652</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NF-DJ01</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NF-TS40</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>VD-250P</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>JR-SQ50NW</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>C2DM-40CP</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>C2DM-40N</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Z2R-400CN4</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DSL-1204-G02M</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>VD-130T</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ET-500PL3</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NF-DM03</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>VD-300</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
+        <is>
+          <t>NF-DA01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2267,10 +3797,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>18154</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
+        <is>
+          <t>ZD-M80P</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2279,10 +3819,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
+        <is>
+          <t>NF-DB02</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2291,10 +3841,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
+        <is>
+          <t>BGS-CM30P</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2303,10 +3863,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
+        <is>
+          <t>C2DM-S80CP</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2315,10 +3885,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>51635</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
+        <is>
+          <t>NF-DE02</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2332,6 +3912,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
+          <t>NF25-D</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
@@ -2339,10 +3929,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
+        <is>
+          <t>MVS-LC05</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2351,10 +3951,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>51635</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
+        <is>
+          <t>D3WF-TP</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2363,10 +3973,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
+        <is>
+          <t>BGS-DL10CN</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2375,10 +3995,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
+        <is>
+          <t>CD22-100-485M122</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2387,10 +4017,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
+        <is>
+          <t>BGS-HL25T2</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2399,10 +4039,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
+        <is>
+          <t>CTD-2500P-R</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2411,10 +4061,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
+        <is>
+          <t>CVSE1-P20-RA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2423,10 +4083,20 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
+        <is>
+          <t>BGS-Z10N</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2435,10 +4105,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
+        <is>
+          <t>LK-S02</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2447,10 +4127,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
+        <is>
+          <t>BA-30TA-S</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2459,10 +4149,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
+        <is>
+          <t>JCN-S</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2471,10 +4171,20 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
+        <is>
+          <t>CTD-2500P-IR</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2483,10 +4193,20 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
+        <is>
+          <t>ZD-M80P-M12</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2495,286 +4215,526 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>VR-800CN</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>V3D-200</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>50952</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MVS-C2S</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MVS-PM-R</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>V2T-7000CDP</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BA-30TC</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JT-H1000CP</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>FASV-EXR5</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BGS-DL70CP</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BGS-CM30CP</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>51144</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ZD-L40P</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>CRDF-100P</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>51400</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ED-100PD3</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>C2RP-F400P</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ED-100PL</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ET-500PD3</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>C2DP-80CN</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ZR-L1000P</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>C2DP-11N</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>53639</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>STL-0H12-G05M</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>C2DP-40CN</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ZD-L40N</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>BA-06TA-S</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
+        <is>
+          <t>BGS-ZM10CP4</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2783,10 +4743,20 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
+        <is>
+          <t>FASV-0813V</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2795,10 +4765,20 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
+        <is>
+          <t>ZT-L3000P</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2807,10 +4787,20 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
+        <is>
+          <t>NF-DW01</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2819,10 +4809,20 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
+        <is>
+          <t>BGS-CM30N</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2831,10 +4831,20 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
+        <is>
+          <t>MVS-C3IO</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2843,10 +4853,20 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
+        <is>
+          <t>BGS-CM30CN</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2855,10 +4875,20 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
+        <is>
+          <t>BL-W130L-1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2867,10 +4897,20 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
+        <is>
+          <t>BRF-CHP</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2879,10 +4919,20 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
+        <is>
+          <t>OPID-122W</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2891,10 +4941,20 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
+        <is>
+          <t>FASV-EXR1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2903,10 +4963,20 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
+        <is>
+          <t>KR-Q300CPW</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2915,10 +4985,20 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
+        <is>
+          <t>BGS-Y8N-M12</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2927,10 +5007,20 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
+        <is>
+          <t>YR-Q39P-M12</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2939,10 +5029,20 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20149</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
+        <is>
+          <t>CDD-40N-IR</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2951,10 +5051,20 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
+        <is>
+          <t>V2RF-N</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2963,10 +5073,20 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
+        <is>
+          <t>NF-TM03</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2975,10 +5095,20 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
+        <is>
+          <t>UC1-CL11</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2987,10 +5117,20 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
+        <is>
+          <t>KR-Q50PW</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2999,10 +5139,20 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
+        <is>
+          <t>BGS-Z10CP</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3011,10 +5161,20 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
+        <is>
+          <t>T000</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3023,10 +5183,20 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
+        <is>
+          <t>Z3R-400P</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3035,10 +5205,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
+        <is>
+          <t>LS-100CP</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3047,10 +5227,20 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
+        <is>
+          <t>P250F</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3059,10 +5249,20 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
+        <is>
+          <t>Z3D-100CP4</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3071,10 +5271,20 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
+        <is>
+          <t>CD33-85NA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3083,10 +5293,20 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
+        <is>
+          <t>CVS-CN</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3095,10 +5315,20 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
+        <is>
+          <t>ZD-W20N</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3107,10 +5337,20 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
+        <is>
+          <t>D3IF-TP</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3119,10 +5359,20 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
+        <is>
+          <t>D3RF-TMN</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3131,10 +5381,20 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
+        <is>
+          <t>NF-DB01-10</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3143,10 +5403,20 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
+        <is>
+          <t>CDA-M</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3155,10 +5425,20 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
+        <is>
+          <t>NF-TB02</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3167,10 +5447,20 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
+        <is>
+          <t>D3RF-TN</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3179,10 +5469,20 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
+        <is>
+          <t>CDD-100P-R</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3191,10 +5491,20 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
+        <is>
+          <t>LK-S01</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3203,10 +5513,20 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
+        <is>
+          <t>TOF-DL250AM12</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3215,10 +5535,20 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
+        <is>
+          <t>CD22-100AC</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3227,10 +5557,20 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
+        <is>
+          <t>CS-30TAC-HT</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3239,10 +5579,20 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
+        <is>
+          <t>D2SA-MP3S</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3251,10 +5601,20 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
+        <is>
+          <t>CD22-35AM12</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3263,10 +5623,20 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
+        <is>
+          <t>NF-DK04</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3275,10 +5645,20 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
+        <is>
+          <t>CD22-15AM12</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3287,10 +5667,20 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
+        <is>
+          <t>Z4D-L09CP4</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3299,10 +5689,20 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
+        <is>
+          <t>NF-DK06</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3311,10 +5711,20 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
+        <is>
+          <t>Z4T-2500-CP4</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3323,10 +5733,20 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
+        <is>
+          <t>D4RF-T</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3335,10 +5755,20 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
+        <is>
+          <t>BRF-N</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3347,10 +5777,20 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
+        <is>
+          <t>JD-HR80CN</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3359,10 +5799,20 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>50827</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
+        <is>
+          <t>PLN-1</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3371,10 +5821,20 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
+        <is>
+          <t>SD-20CP</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3383,10 +5843,20 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
+        <is>
+          <t>V2R-1200DN</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3395,10 +5865,20 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
+        <is>
+          <t>SR-150P</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3407,10 +5887,20 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
+        <is>
+          <t>ST-400CP</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3419,10 +5909,20 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
+        <is>
+          <t>Z3T-2500CP4</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3431,18 +5931,728 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t>16398</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>BGS-DL25TCN</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>18139</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>BGS-2V50CP</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>15795</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DSR-5000</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>17755</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MVS-DP-E</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>15729</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ZT-1200CP</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>16406</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MVS-DP</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>51622</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>NF-DB06</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>17726</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>C2DM-S40CP</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>51681</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>NF-TG02</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>15702</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ZR-Q200P</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>15297</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DSD-100</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>12167</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>KR-Q50CN</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>51400</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>FASV-EXR-LT2</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>51685</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>NF-TH08</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>17507</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ZT-M3000CP4</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>52658</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>CVS-C2Y</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>15515</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CRDF-100CP</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>15505</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CRD-300CP</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>53102</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>FASV-03514V</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>13996</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>JT-S1000PR</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>13980</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>JR-H300P</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>BGS-ZM10P</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>51733</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NF-DA07</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>17183</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>CVS4-P40W-R</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>17125</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>C2RM-350CP</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>16831</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Z2T-2000CN4</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>17113</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>C2DM-11CP</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>50988</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>FASV-EXR05</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>17109</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>C2TP-2000CP</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>15385</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ED-100PD</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
           <t>12115</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr"/>
-      <c r="B252" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KR-Q50N</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>13880</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>VT-4000</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SA-80T-4IO</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>OPTEX</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/existenciasOptex.xlsx
+++ b/excel/existenciasOptex.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Linea</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Existencias</t>
         </is>
